--- a/configs/models_to_test.xlsx
+++ b/configs/models_to_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jason\OneDrive\文档\GitHub\fr-analysis\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jason\OneDrive\Desktop\Research\UBC\ProjectKickoff\ATC138Comparison_tests_\atc138-testing-postrelease\atc138-testing-workflow\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00F86E5-738B-4134-A7F9-C97A3AEBD99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5E7890-402C-48BD-9AB6-4496762051A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F5F1FA4-9B25-4F82-8B27-64E924962748}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>model</t>
   </si>
@@ -206,9 +206,6 @@
     <t>1967_W2b_3_IM5</t>
   </si>
   <si>
-    <t>1985_W1a_1_IM1</t>
-  </si>
-  <si>
     <t>1985_W1a_1_IM2</t>
   </si>
   <si>
@@ -219,6 +216,30 @@
   </si>
   <si>
     <t>1985_W1a_1_IM5</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM1</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM2</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM3</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM4</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM5</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM6</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM7</t>
+  </si>
+  <si>
+    <t>1985_W1a_2_IM8</t>
   </si>
 </sst>
 </file>
@@ -708,10 +729,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1087,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F93FED4-3570-48B5-B751-6F8E95F5C203}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -1096,10 +1115,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1107,10 +1126,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="b">
@@ -1119,10 +1138,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="b">
@@ -1131,10 +1150,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="b">
@@ -1143,10 +1162,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="b">
@@ -1155,661 +1174,745 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>47</v>
       </c>
       <c r="C6" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>48</v>
       </c>
       <c r="C7" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>49</v>
       </c>
       <c r="C8" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>50</v>
       </c>
       <c r="C9" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>51</v>
       </c>
       <c r="C10" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>52</v>
       </c>
       <c r="C11" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>53</v>
       </c>
       <c r="C12" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>54</v>
       </c>
       <c r="C13" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>55</v>
       </c>
       <c r="C14" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>56</v>
       </c>
       <c r="C15" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>58</v>
       </c>
       <c r="C17" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>59</v>
       </c>
       <c r="C18" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>60</v>
       </c>
       <c r="C19" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>61</v>
       </c>
       <c r="C20" t="b">
-        <f>FALSE</f>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C21" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="C28" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="C55" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="C56" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="C57" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="C58" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="C59" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="C60" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="C61" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="C62" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="C63" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="C64" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="C65" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="C66" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C60" t="b">
+      <c r="C67" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
